--- a/artfynd/A 25206-2026 artfynd.xlsx
+++ b/artfynd/A 25206-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>114820194</v>
       </c>
       <c r="B2" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,12 +775,7 @@
         <v>114819873</v>
       </c>
       <c r="B3" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,12 +872,7 @@
         <v>114819874</v>
       </c>
       <c r="B4" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,12 +969,7 @@
         <v>114819295</v>
       </c>
       <c r="B5" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,12 +1066,7 @@
         <v>114819412</v>
       </c>
       <c r="B6" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
